--- a/samples/3_scan_testfaelle.xlsx
+++ b/samples/3_scan_testfaelle.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>4014819072508</t>
+          <t>4014819072505</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>4012345678901</t>
+          <t>4012345678902</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
